--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2023_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2023_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>8.954499591715926</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>16.22560068925514</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>11.76136059904818</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>11.03701182131633</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>7.682408393131479</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>10.82506758378468</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>11.39975939640043</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>9.718185063852914</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>9.357504068299916</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>10.87346090774677</v>
       </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>10.65604746383115</v>
       </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -646,9 +608,6 @@
       </c>
       <c r="E13">
         <v>15.76863767410175</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2023_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2023_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -423,190 +423,209 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B4">
-        <v>306494.78</v>
+        <v>332405.09</v>
       </c>
       <c r="C4">
-        <v>274240.38</v>
+        <v>302557.97</v>
       </c>
       <c r="D4">
-        <v>32254.40000000002</v>
+        <v>29847.12000000005</v>
       </c>
       <c r="E4">
-        <v>11.76136059904818</v>
+        <v>9.864926050369792</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="B5">
-        <v>278332.78</v>
+        <v>306494.78</v>
       </c>
       <c r="C5">
-        <v>250666.67</v>
+        <v>274240.38</v>
       </c>
       <c r="D5">
-        <v>27666.11000000002</v>
+        <v>32254.40000000002</v>
       </c>
       <c r="E5">
-        <v>11.03701182131633</v>
+        <v>11.76136059904818</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="B6">
-        <v>275542.56</v>
+        <v>278332.78</v>
       </c>
       <c r="C6">
-        <v>255884.47</v>
+        <v>250666.67</v>
       </c>
       <c r="D6">
-        <v>19658.09</v>
+        <v>27666.11000000002</v>
       </c>
       <c r="E6">
-        <v>7.682408393131479</v>
+        <v>11.03701182131633</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="B7">
-        <v>274923.59</v>
+        <v>275542.56</v>
       </c>
       <c r="C7">
-        <v>248069.86</v>
+        <v>255884.47</v>
       </c>
       <c r="D7">
-        <v>26853.73000000004</v>
+        <v>19658.09</v>
       </c>
       <c r="E7">
-        <v>10.82506758378468</v>
+        <v>7.682408393131479</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B8">
-        <v>266327.56</v>
+        <v>274923.59</v>
       </c>
       <c r="C8">
-        <v>239073.73</v>
+        <v>248069.86</v>
       </c>
       <c r="D8">
-        <v>27253.82999999999</v>
+        <v>26853.73000000004</v>
       </c>
       <c r="E8">
-        <v>11.39975939640043</v>
+        <v>10.82506758378468</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="B9">
-        <v>263644.12</v>
+        <v>266327.56</v>
       </c>
       <c r="C9">
-        <v>240292.09</v>
+        <v>239073.73</v>
       </c>
       <c r="D9">
-        <v>23352.03</v>
+        <v>27253.82999999999</v>
       </c>
       <c r="E9">
-        <v>9.718185063852914</v>
+        <v>11.39975939640043</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="B10">
-        <v>240216.64</v>
+        <v>263644.12</v>
       </c>
       <c r="C10">
-        <v>219661.78</v>
+        <v>240292.09</v>
       </c>
       <c r="D10">
-        <v>20554.86000000002</v>
+        <v>23352.03</v>
       </c>
       <c r="E10">
-        <v>9.357504068299916</v>
+        <v>9.718185063852914</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Corral</t>
         </is>
       </c>
       <c r="B11">
-        <v>232590.69</v>
+        <v>240216.64</v>
       </c>
       <c r="C11">
-        <v>209780.31</v>
+        <v>219661.78</v>
       </c>
       <c r="D11">
-        <v>22810.38</v>
+        <v>20554.86000000002</v>
       </c>
       <c r="E11">
-        <v>10.87346090774677</v>
+        <v>9.357504068299916</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="B12">
-        <v>231615.7</v>
+        <v>232590.69</v>
       </c>
       <c r="C12">
-        <v>209311.38</v>
+        <v>209780.31</v>
       </c>
       <c r="D12">
-        <v>22304.32000000001</v>
+        <v>22810.38</v>
       </c>
       <c r="E12">
-        <v>10.65604746383115</v>
+        <v>10.87346090774677</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>231615.7</v>
+      </c>
+      <c r="C13">
+        <v>209311.38</v>
+      </c>
+      <c r="D13">
+        <v>22304.32000000001</v>
+      </c>
+      <c r="E13">
+        <v>10.65604746383115</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Lago Ranco</t>
         </is>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>214240.48</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>185059.17</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>29181.31</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>15.76863767410175</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2023_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2023_los_rios.xlsx
@@ -636,7 +636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -645,50 +645,33 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Corral</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>240216.64</v>
+          <t>La Unión</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Futrono</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>231615.7</v>
+          <t>Los Lagos</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>La Unión</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>306494.78</v>
+          <t>Máfil</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lago Ranco</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>214240.48</v>
+          <t>Paillaco</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -697,28 +680,19 @@
           <t>Lanco</t>
         </is>
       </c>
-      <c r="B6">
-        <v>275542.56</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>274923.59</v>
+          <t>Panguipulli</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Máfil</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>263644.12</v>
+          <t>Río Bueno</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -727,48 +701,33 @@
           <t>Mariquina</t>
         </is>
       </c>
-      <c r="B9">
-        <v>278332.78</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paillaco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>266327.56</v>
+          <t>Corral</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>232590.69</v>
+          <t>Valdivia</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>393692</v>
+          <t>Lago Ranco</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>411323.97</v>
+          <t>Futrono</t>
+        </is>
       </c>
     </row>
   </sheetData>
